--- a/data/Anotasi Skill (Kappa).xlsx
+++ b/data/Anotasi Skill (Kappa).xlsx
@@ -531,7 +531,8 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>c#
+          <t>programming language
+c#
 java
 php
 erp
@@ -539,30 +540,32 @@
 mysql
 sql server
 postgresql
+object-oriented programming
 development tools
 oop
 git
 visual studio
+communication
 information engineering</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5</v>
+        <v>0.5909</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8462</v>
+        <v>0.8125</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6286</v>
+        <v>0.6842</v>
       </c>
     </row>
     <row r="3">
@@ -635,12 +638,11 @@
 regression testing
 usability testing
 quality assurance
-application testing
 selenium
-appium
 postman
 critical thinking
-responsible
+analytical
+english
 ownership</t>
         </is>
       </c>
@@ -651,16 +653,16 @@
         <v>22</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0.3125</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8333</v>
+        <v>0.9091</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4545</v>
+        <v>0.4651</v>
       </c>
     </row>
     <row r="4">
@@ -712,13 +714,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>engineering
+          <t>information technology
+engineering
+object-oriented programming
 asp.net
 sql
 c#
+razor
 html
 web services
+wcf
+rest
+soap
 web api
+api
 t-sql
 application lifecycle management
 vsts
@@ -730,26 +739,27 @@
 telerik
 self-motivated
 accountability
-ownership</t>
+ownership
+mcsd</t>
         </is>
       </c>
       <c r="E4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F4" t="n">
         <v>10</v>
       </c>
-      <c r="F4" t="n">
-        <v>14</v>
-      </c>
       <c r="G4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4167</v>
+        <v>0.5833</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5263</v>
+        <v>0.5185</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4651</v>
+        <v>0.549</v>
       </c>
     </row>
     <row r="5">
@@ -791,32 +801,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>web applications
-programming languages
+          <t>programming languages
 sql
 sql database
 relational database
 curiosity
-ai technologies</t>
+scalable</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2857</v>
+        <v>0.3571</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5714</v>
+        <v>0.8333</v>
       </c>
       <c r="J5" t="n">
-        <v>0.381</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">
@@ -866,36 +875,36 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ad hoc reports
-data processing
+          <t>data processing
 analytical enhancements
 management
 business
 industrial engineering
 data analysis
 microsoft excel
-excel macros
 vba
+communication
+english
 analysis workflow</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2857</v>
+        <v>0.3333</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5455</v>
+        <v>0.6364</v>
       </c>
       <c r="J6" t="n">
-        <v>0.375</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="7">
@@ -939,31 +948,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>mobile app development
+          <t>web app
+mobile app
+collaborating
+analytical
 time management
-server-side applications
-apis
+scalable
+high performance
 databases
 system architecture</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F7" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1111</v>
+        <v>0.4444</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3333</v>
+        <v>0.8889</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1667</v>
+        <v>0.5926</v>
       </c>
     </row>
     <row r="8">
@@ -1008,36 +1020,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>social media crawler
-data quality
+          <t>data quality
+communicate
 sql
 programming languages
 javascript
+node
 python
 mariadb
 redis
 kafka
 elasticsearch
-data acquisition</t>
+linux
+data acquisition
+api</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5</v>
+        <v>0.7222</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8182</v>
+        <v>0.9286</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6207</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="9">
@@ -1095,38 +1110,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>it auditing
-it governance
-risk management
+          <t>risk management
 it compliance
 network security
-information security
-it systems
-software programming
+information technology
 system control
 penetration testing
-it systems
-it controls
+communication
+analytical
+audits
 risk assessment</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>0.24</v>
+        <v>0.32</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3243</v>
+        <v>0.4571</v>
       </c>
     </row>
     <row r="10">
@@ -1265,31 +1277,34 @@
         <is>
           <t>rdbms
 postgresql
-ms sql server
 mysql
 git
+agile
+scrum
 rabbitmq
 kafka
+analytical
+communication
 engineering</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F11" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
         <v>4</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2222</v>
+        <v>0.3889</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>0.6364</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3077</v>
+        <v>0.4828</v>
       </c>
     </row>
     <row r="12">
@@ -1358,7 +1373,8 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>python
+          <t>django
+python
 git
 sql
 nosql
@@ -1368,28 +1384,29 @@
 redis
 memcached
 fastapi
-reusable code
 scalability
-clean code</t>
+clean code
+maintainable code
+software development</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F12" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G12" t="n">
         <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>0.303</v>
+        <v>0.3636</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7692</v>
+        <v>0.8</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4348</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="13">
@@ -1447,40 +1464,37 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>it sysadmin
-it operations
-it systems
-server
+          <t>information technology
+software engineering
+operating system
 scripting
 cli
 sql
 data security
+cyber security
 mikrotik
 vm
-ha
-enterprise backup solution
 it infrastructure
-firewall
 vps</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G13" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2083</v>
+        <v>0.375</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3333</v>
+        <v>0.75</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2564</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="14">
@@ -1550,34 +1564,36 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data analyst
-bi engineer
+          <t>bi engineer
 sql
 relational database
 bi tools
 power bi
 looker
+etl
 data architecture
-data governance</t>
+data governance
+communication
+agile</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G14" t="n">
         <v>5</v>
       </c>
       <c r="H14" t="n">
-        <v>0.129</v>
+        <v>0.1935</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4444</v>
+        <v>0.5455</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2</v>
+        <v>0.2857</v>
       </c>
     </row>
     <row r="15">
@@ -1635,34 +1651,36 @@
       <c r="D15" t="inlineStr">
         <is>
           <t>system testing
-system integration test
 java
+banking
 microservice
+api
 postgresql
 mysql
+communication
 software security
 code testing
-bug troubleshooting
+troubleshooting
 application support</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2609</v>
+        <v>0.4348</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6</v>
+        <v>0.8333</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3636</v>
+        <v>0.5714</v>
       </c>
     </row>
     <row r="16">
@@ -1701,26 +1719,32 @@
       <c r="D16" t="inlineStr">
         <is>
           <t>software testing
-qa testing</t>
+qa testing
+bug tracking
+test case
+software development
+test automation
+analytical
+information technology</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F16" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>0.875</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1667</v>
+        <v>0.7778</v>
       </c>
     </row>
     <row r="17">
@@ -1762,30 +1786,32 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>desktop support
+          <t>english
+desktop support
 cloud technology
 it security
+troubleshooting
 software support
 project support</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2222</v>
+        <v>0.3333</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4</v>
+        <v>0.4286</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2857</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="18">
@@ -1845,8 +1871,8 @@
       <c r="D18" t="inlineStr">
         <is>
           <t>user research
-interactive prototype
 usability testing
+design system
 design specification
 figma
 adobe illustrator
@@ -1855,22 +1881,22 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="I18" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4286</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="19">
@@ -1996,26 +2022,29 @@
 angular
 flutter
 java
-rest api</t>
+rest api
+troubleshooting
+information technology
+collaborative</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F20" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G20" t="n">
         <v>3</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1905</v>
+        <v>0.3333</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5714</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2857</v>
+        <v>0.4516</v>
       </c>
     </row>
     <row r="21">
@@ -2055,28 +2084,30 @@
       <c r="D21" t="inlineStr">
         <is>
           <t>network troubleshooting
+troubleshooting
 security monitoring
+information technology
 network routing
 switching</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1667</v>
+        <v>0.25</v>
       </c>
       <c r="I21" t="n">
         <v>0.5</v>
       </c>
       <c r="J21" t="n">
-        <v>0.25</v>
+        <v>0.3333</v>
       </c>
     </row>
   </sheetData>
@@ -2090,7 +2121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B466"/>
+  <dimension ref="A1:B456"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2148,7 +2179,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>actionable insight</t>
+          <t>ad hoc</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2162,13 +2193,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>adaptability</t>
+          <t>adapt</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2212,13 +2243,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>agile development environment</t>
+          <t>agile scrum</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2228,7 +2259,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>agile methodolofy</t>
+          <t>agile scrum framework</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2238,7 +2269,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>agile scrum</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2248,7 +2279,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>agile scrum framework</t>
+          <t>ai technologies</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2258,7 +2289,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>analysis</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2268,27 +2299,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ai frameworks</t>
+          <t>analysis workflow</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ai libraries</t>
+          <t>analytical</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>0.6923076923076923</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ai technologies</t>
+          <t>analytical enhancements</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2298,7 +2329,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>analysis</t>
+          <t>analytical skill</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2308,17 +2339,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>analysis workflow</t>
+          <t>analytical skills</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>analytical</t>
+          <t>analyze</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2328,17 +2359,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>analytical enhancements</t>
+          <t>analyze data</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>analytical skill</t>
+          <t>analyze test</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2348,37 +2379,37 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>analytical skills</t>
+          <t>angular</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>analyze</t>
+          <t>angularjs</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>analyze data</t>
+          <t>api</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.05263157894736836</v>
+        <v>0.7727272727272727</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>analyze operational need</t>
+          <t>apis</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2388,7 +2419,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>analyze test</t>
+          <t>app maintenance</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2398,57 +2429,57 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>angular</t>
+          <t>appium</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>angularjs</t>
+          <t>application</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>application lifecycle management</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.4594594594594595</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>api-based data consumption</t>
+          <t>application support</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>apis</t>
+          <t>application testing</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>app maintenance</t>
+          <t>apps development</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -2458,27 +2489,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>app monitoring</t>
+          <t>asp.net</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>appium</t>
+          <t>asp.net mvc</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>attention to detail</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2488,27 +2519,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>application lifecycle management</t>
+          <t>audit reports</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>application support</t>
+          <t>auditing</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>application testing</t>
+          <t>audits</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -2518,17 +2549,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>apps development</t>
+          <t>automate</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>-0.05263157894736836</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>asp.net</t>
+          <t>automated testing</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -2538,7 +2569,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>asp.net mvc (razor)</t>
+          <t>automation</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2548,7 +2579,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>attention to detail</t>
+          <t>back end</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -2558,17 +2589,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>audit reports</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>-0.05263157894736836</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>auditing principles</t>
+          <t>backend developer</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -2578,7 +2609,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>audits</t>
+          <t>backup solution</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2588,27 +2619,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>automate</t>
+          <t>banking</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>automated testing</t>
+          <t>based system</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>automation</t>
+          <t>basic technical terms</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -2618,7 +2649,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>automation tools</t>
+          <t>basic troubleshooting</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2628,7 +2659,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>back end</t>
+          <t>best practices</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -2638,27 +2669,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>backend</t>
+          <t>bi engineer</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>backend developer</t>
+          <t>bi tools</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>backend development</t>
+          <t>bug fixing</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2668,27 +2699,27 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>banking</t>
+          <t>bug reports</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>baremetal</t>
+          <t>bug tracking</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>basic technical terms</t>
+          <t>bug troubleshooting</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -2698,7 +2729,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>basic troubleshooting</t>
+          <t>bugs system</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -2708,17 +2739,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>best practice</t>
+          <t>business</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>best practices</t>
+          <t>business it</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -2728,27 +2759,27 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>bi engineer</t>
+          <t>business it support</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>bi tools</t>
+          <t>business needs</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>bug fixing</t>
+          <t>business requirements</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -2758,27 +2789,27 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>bug reports</t>
+          <t>business use cases</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>bug tracking</t>
+          <t>c#</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>bug tracking skill</t>
+          <t>cache</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -2788,17 +2819,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>bug troubleshooting</t>
+          <t>cache handling</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>business</t>
+          <t>canva</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -2808,37 +2839,37 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>business it</t>
+          <t>clean code</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0</v>
+        <v>0.6428571428571428</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>business it support</t>
+          <t>cli</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>business needs</t>
+          <t>cloud technology</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>business requirements</t>
+          <t>code review</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -2848,7 +2879,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>business use cases</t>
+          <t>code reviews</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -2858,7 +2889,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>c#</t>
+          <t>code testing</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -2868,7 +2899,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>cache</t>
+          <t>coding</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -2878,57 +2909,57 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>cache handling</t>
+          <t>collaborate</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0</v>
+        <v>-0.0714285714285714</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>canva</t>
+          <t>collaborated</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>clean code</t>
+          <t>collaborating</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6428571428571428</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>cli</t>
+          <t>collaboration</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>cloud technology</t>
+          <t>collaborative</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1</v>
+        <v>0.4594594594594595</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>code review</t>
+          <t>collaboratively</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -2938,27 +2969,27 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>code reviews</t>
+          <t>communicate</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>code testing</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1</v>
+        <v>0.411764705882353</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>coding</t>
+          <t>communication information technology</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -2968,7 +2999,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>collaborate</t>
+          <t>communication skill</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -2978,7 +3009,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>collaborating</t>
+          <t>communication skills</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -2988,7 +3019,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>collaboration</t>
+          <t>compile</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -2998,17 +3029,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>collaborative</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.178082191780822</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>collect data</t>
+          <t>computer engineering</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -3018,17 +3049,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>communicate</t>
+          <t>computer science</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0</v>
+        <v>0.2380952380952381</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>communication</t>
+          <t>computer science fundamentals</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -3038,7 +3069,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>communication information technology</t>
+          <t>concistency</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -3048,7 +3079,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>communication skill</t>
+          <t>continuous integration</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -3058,7 +3089,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>communication skills</t>
+          <t>coordination</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -3068,7 +3099,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>computer</t>
+          <t>crawler</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -3078,7 +3109,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>computer engineering</t>
+          <t>creating design system</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -3088,17 +3119,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>computer science</t>
+          <t>critical thinking</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.06542056074766345</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>computer science fundamentals</t>
+          <t>cross functional teams</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -3108,27 +3139,27 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>concistency</t>
+          <t>css</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>continuous integration</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>core banking</t>
+          <t>customer relationship menagement</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -3138,7 +3169,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>core loan</t>
+          <t>customer support</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -3148,17 +3179,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>crawler</t>
+          <t>cyber security</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>creating design system</t>
+          <t>cybersecurity</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -3168,17 +3199,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>critical thinking</t>
+          <t>cybesecurity</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>cross functional teams</t>
+          <t>dashboards</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -3188,7 +3219,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>cross-functional teams</t>
+          <t>data</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -3198,7 +3229,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>css</t>
+          <t>data acquisition</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -3208,17 +3239,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>curiosity</t>
+          <t>data analysis</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1</v>
+        <v>0.6428571428571428</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>customer relationship menagement</t>
+          <t>data analyst</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -3228,37 +3259,37 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>customer support</t>
+          <t>data architecture</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>cyber security</t>
+          <t>data engineers</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>cyber security basic</t>
+          <t>data governance</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>cybersecurity</t>
+          <t>data modeling</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -3268,7 +3299,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>cybesecurity</t>
+          <t>data modelling</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -3278,27 +3309,27 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>data acquisition</t>
+          <t>data operations</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>data analysis</t>
+          <t>data pipelines</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>data analyst</t>
+          <t>data preprocessing</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -3308,7 +3339,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>data architecture</t>
+          <t>data processing</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -3318,27 +3349,27 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>data engineering</t>
+          <t>data quality</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>data engineers</t>
+          <t>data requirements</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>data governance</t>
+          <t>data security</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -3348,17 +3379,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>data modeling</t>
+          <t>data structures</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>data modelling</t>
+          <t>data warehousing</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -3368,7 +3399,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>data operations</t>
+          <t>data warehousing concepts</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -3378,7 +3409,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>data pipelines</t>
+          <t>database</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -3388,7 +3419,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>data preprocessing</t>
+          <t>database logic</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -3398,7 +3429,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>data processing</t>
+          <t>databases</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -3408,47 +3439,47 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>data quality</t>
+          <t>datasets</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>data requirements</t>
+          <t>deep learning</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>data security</t>
+          <t>deploy</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>data structures</t>
+          <t>design</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>data warehouse</t>
+          <t>design decision</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -3458,7 +3489,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>data warehousing</t>
+          <t>design guidelines</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -3468,7 +3499,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>database</t>
+          <t>design ideas</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -3478,27 +3509,27 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>database logic</t>
+          <t>design patterns</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>databases</t>
+          <t>design principles</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>deep learning</t>
+          <t>design specification</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -3508,17 +3539,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>deploy</t>
+          <t>design system</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>design tools</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -3528,17 +3559,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>design decision</t>
+          <t>desktop support</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>design guidelines</t>
+          <t>develop</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -3548,7 +3579,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>design ideas</t>
+          <t>development environment</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -3558,47 +3589,47 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>design operational need</t>
+          <t>development tools</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>design patterns</t>
+          <t>django</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>design principles</t>
+          <t>docker</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>-0.05263157894736836</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>design specification</t>
+          <t>documenting design</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>design system</t>
+          <t>effective collaboration</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -3608,47 +3639,47 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>design tools</t>
+          <t>elasticsearch</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>desktop support</t>
+          <t>electrical engineering</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>develop</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0</v>
+        <v>0.6428571428571428</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>develop documentation</t>
+          <t>english</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0</v>
+        <v>0.4594594594594595</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>develop operatioanl need</t>
+          <t>english proficiency</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -3658,17 +3689,17 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>development tools</t>
+          <t>enterprise backup solution</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>django</t>
+          <t>enterprise resource planning</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -3678,37 +3709,37 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>django framework</t>
+          <t>erp</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>docker</t>
+          <t>erp-based applications</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>documenting</t>
+          <t>etl</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>effective collaboration</t>
+          <t>excel macro</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -3718,17 +3749,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>elasticsearch</t>
+          <t>excel macros</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>electrical engineering</t>
+          <t>fast-paced</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -3738,17 +3769,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>engineering</t>
+          <t>fastapi</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.6428571428571428</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>english</t>
+          <t>feature development</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -3758,17 +3789,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>english proficiency</t>
+          <t>figma</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>enhance stability</t>
+          <t>firewall</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -3778,17 +3809,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>enterprise backup solution</t>
+          <t>firewalls</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>enterprise resource planning</t>
+          <t>fix</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -3798,17 +3829,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>erp</t>
+          <t>fix programming bugs</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>erp-based applications</t>
+          <t>flexible</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -3818,17 +3849,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>etl</t>
+          <t>flutter</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>etl process</t>
+          <t>front end</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -3838,17 +3869,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>excel macros</t>
+          <t>frontend</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>fast-paced</t>
+          <t>full-stack development</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -3858,47 +3889,47 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>fastapi</t>
+          <t>fullstack development</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>feature development</t>
+          <t>git</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>figma</t>
+          <t>governance risk</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>firewall</t>
+          <t>graphic desi</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>fix</t>
+          <t>graphic design tool</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -3908,7 +3939,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>fix programming bugs</t>
+          <t>ha</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -3918,7 +3949,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>flexible</t>
+          <t>hardware</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -3928,7 +3959,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>fluent in english</t>
+          <t>hardware support</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -3938,47 +3969,47 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>flutter</t>
+          <t>hardwares</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>front end</t>
+          <t>high performance</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>frontend</t>
+          <t>html</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>full-stack development</t>
+          <t>http protocol</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>fullstack development</t>
+          <t>identify bugs</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -3988,17 +4019,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>git</t>
+          <t>implement</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>graphic desi</t>
+          <t>indepedently</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -4008,7 +4039,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>graphic design tool</t>
+          <t>indonesian</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -4018,7 +4049,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ha</t>
+          <t>industrial engineering</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -4028,27 +4059,27 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>informatics engineering</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>-0.05263157894736836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>hardware support</t>
+          <t>information engineering</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0</v>
+        <v>0.6428571428571428</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>hardwares</t>
+          <t>information security</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -4058,17 +4089,17 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>high performance</t>
+          <t>information system</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0</v>
+        <v>-0.0714285714285714</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>high-fidelity wireframe</t>
+          <t>information systems</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -4078,37 +4109,37 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>high-performance systems</t>
+          <t>information technology</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>0</v>
+        <v>0.3055555555555555</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>html</t>
+          <t>information tehnology</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>http protocol</t>
+          <t>infrastructure</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>identify bugs</t>
+          <t>initiatives</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -4118,7 +4149,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>implement</t>
+          <t>installation</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -4128,7 +4159,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>indepedently</t>
+          <t>interactive prototype</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -4138,7 +4169,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>independent work</t>
+          <t>interpersonal</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -4148,7 +4179,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>indonesian</t>
+          <t>interpersonal skills</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -4158,17 +4189,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>industrial engineering</t>
+          <t>ip segmentation</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>informatics engineering</t>
+          <t>ip segments</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -4178,17 +4209,17 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>information engineering</t>
+          <t>it auditing</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>0.6428571428571428</v>
+        <v>0</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>information security</t>
+          <t>it compliance</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -4198,7 +4229,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>information system</t>
+          <t>it controls</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -4208,7 +4239,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>information systems</t>
+          <t>it governance</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -4218,17 +4249,17 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>information technology</t>
+          <t>it infrastructure</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>information tehnology</t>
+          <t>it operation</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -4238,7 +4269,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>infrastructure</t>
+          <t>it operation monitoring</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -4248,7 +4279,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>initiatives</t>
+          <t>it operations</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -4258,27 +4289,27 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>installation</t>
+          <t>it security</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>interactive prototype</t>
+          <t>it sysadmin</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>interpersonal</t>
+          <t>it systems</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -4288,7 +4319,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>interpersonal skills</t>
+          <t>it technologies</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -4298,27 +4329,27 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ip segmentation</t>
+          <t>java</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>ip segments</t>
+          <t>javascript</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>0</v>
+        <v>0.8275862068965517</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>it auditing</t>
+          <t>jquery</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -4328,7 +4359,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>it compliance</t>
+          <t>kafka</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -4338,17 +4369,17 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>it controls</t>
+          <t>key-value database</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>it department policy</t>
+          <t>l1</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -4358,27 +4389,27 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>it governance</t>
+          <t>l2 support</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>it infrastructure</t>
+          <t>large-scale systems</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>it operation</t>
+          <t>libraries</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -4388,37 +4419,37 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>it operation monitoring</t>
+          <t>linux</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0</v>
+        <v>0.6428571428571428</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>it operations</t>
+          <t>linux development environment</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>it security</t>
+          <t>loan</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>it sysadmin</t>
+          <t>looker</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -4428,17 +4459,17 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>it systems</t>
+          <t>machine learning</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>0.6428571428571428</v>
+        <v>1</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>it technologies</t>
+          <t>maintain</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -4448,37 +4479,37 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>it tools</t>
+          <t>maintainable code</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>0</v>
+        <v>0.6428571428571428</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>java</t>
+          <t>manage databases</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>javascript</t>
+          <t>manage documentation</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>0.8275862068965517</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>jquery</t>
+          <t>management</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -4488,17 +4519,17 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>kafka</t>
+          <t>management needs</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>key-value database</t>
+          <t>managing multiple task</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -4508,7 +4539,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>l1</t>
+          <t>manual testing</t>
         </is>
       </c>
       <c r="B242" t="n">
@@ -4518,37 +4549,37 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>l2 support</t>
+          <t>mariadb</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>large-scale systems</t>
+          <t>mcsd</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>libraries</t>
+          <t>memcached</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>linux</t>
+          <t>meraki</t>
         </is>
       </c>
       <c r="B246" t="n">
@@ -4558,7 +4589,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>linux development environment</t>
+          <t>message broker</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -4568,7 +4599,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>linux environments</t>
+          <t>message brokers</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -4578,17 +4609,17 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>linux-based systems</t>
+          <t>microservice</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>looker</t>
+          <t>microsoft excel</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -4598,27 +4629,27 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>low-fidelity wireframe</t>
+          <t>mikrotik</t>
         </is>
       </c>
       <c r="B251" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>machine learning</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="B252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>maintain</t>
+          <t>ml pipelines</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -4628,17 +4659,17 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>maintainable code</t>
+          <t>mlops</t>
         </is>
       </c>
       <c r="B254" t="n">
-        <v>-0.05263157894736836</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>maintaining design system</t>
+          <t>mobile</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -4648,37 +4679,37 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>manage databases</t>
+          <t>mobile app</t>
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>management</t>
+          <t>mobile app development</t>
         </is>
       </c>
       <c r="B257" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>management needs</t>
+          <t>model deployment</t>
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>managing multiple task</t>
+          <t>model monitoring</t>
         </is>
       </c>
       <c r="B259" t="n">
@@ -4688,7 +4719,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>manual testing</t>
+          <t>model optimization</t>
         </is>
       </c>
       <c r="B260" t="n">
@@ -4698,17 +4729,17 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>mariadb</t>
+          <t>model validation</t>
         </is>
       </c>
       <c r="B261" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>massage broker</t>
+          <t>modern javascript framework</t>
         </is>
       </c>
       <c r="B262" t="n">
@@ -4718,7 +4749,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>mcsd</t>
+          <t>monitor</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -4728,7 +4759,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>mcsd web application</t>
+          <t>monitoring</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -4738,17 +4769,17 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>memcached</t>
+          <t>ms sql server</t>
         </is>
       </c>
       <c r="B265" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>meraki</t>
+          <t>mvc</t>
         </is>
       </c>
       <c r="B266" t="n">
@@ -4758,37 +4789,37 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>message brokers</t>
+          <t>mysql</t>
         </is>
       </c>
       <c r="B267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>microservice</t>
+          <t>network</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>microsoft excel</t>
+          <t>network operation system</t>
         </is>
       </c>
       <c r="B269" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>mikrotik</t>
+          <t>network routing</t>
         </is>
       </c>
       <c r="B270" t="n">
@@ -4798,17 +4829,17 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>minimal supervision</t>
+          <t>network security</t>
         </is>
       </c>
       <c r="B271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>network support</t>
         </is>
       </c>
       <c r="B272" t="n">
@@ -4818,17 +4849,17 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>ml pipelines</t>
+          <t>network troubleshooting</t>
         </is>
       </c>
       <c r="B273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>mlops</t>
+          <t>node</t>
         </is>
       </c>
       <c r="B274" t="n">
@@ -4838,17 +4869,17 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>mobile</t>
+          <t>nosql</t>
         </is>
       </c>
       <c r="B275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>mobile app</t>
+          <t>object orient programming</t>
         </is>
       </c>
       <c r="B276" t="n">
@@ -4858,17 +4889,17 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>mobile app development</t>
+          <t>object-oriented programming</t>
         </is>
       </c>
       <c r="B277" t="n">
-        <v>1</v>
+        <v>0.6428571428571428</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>model deployment</t>
+          <t>oop</t>
         </is>
       </c>
       <c r="B278" t="n">
@@ -4878,17 +4909,17 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>model monitoring</t>
+          <t>operating system</t>
         </is>
       </c>
       <c r="B279" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>model optimization</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="B280" t="n">
@@ -4898,7 +4929,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>model validation</t>
+          <t>operations</t>
         </is>
       </c>
       <c r="B281" t="n">
@@ -4908,7 +4939,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>modern javascript framework</t>
+          <t>optimize</t>
         </is>
       </c>
       <c r="B282" t="n">
@@ -4918,7 +4949,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>monitor</t>
+          <t>organizational</t>
         </is>
       </c>
       <c r="B283" t="n">
@@ -4928,7 +4959,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>monitoring</t>
+          <t>organizational skill</t>
         </is>
       </c>
       <c r="B284" t="n">
@@ -4938,47 +4969,47 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>ms sql server</t>
+          <t>ownership</t>
         </is>
       </c>
       <c r="B285" t="n">
-        <v>1</v>
+        <v>0.6428571428571428</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>mvc</t>
+          <t>penetration testing</t>
         </is>
       </c>
       <c r="B286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>mysql</t>
+          <t>performance optimization</t>
         </is>
       </c>
       <c r="B287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>php</t>
         </is>
       </c>
       <c r="B288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>network operation system</t>
+          <t>pipelines</t>
         </is>
       </c>
       <c r="B289" t="n">
@@ -4988,37 +5019,37 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>network routing</t>
+          <t>plan</t>
         </is>
       </c>
       <c r="B290" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>network security</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="B291" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>network support</t>
+          <t>postgresql</t>
         </is>
       </c>
       <c r="B292" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>network troubleshooting</t>
+          <t>postman</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -5028,17 +5059,17 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>node</t>
+          <t>power bi</t>
         </is>
       </c>
       <c r="B294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>node.js</t>
+          <t>preprocess</t>
         </is>
       </c>
       <c r="B295" t="n">
@@ -5048,17 +5079,17 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>nosql</t>
+          <t>presentation design</t>
         </is>
       </c>
       <c r="B296" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>object-oriented programming</t>
+          <t>prioritize</t>
         </is>
       </c>
       <c r="B297" t="n">
@@ -5068,17 +5099,17 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>oop</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="B298" t="n">
-        <v>0.6428571428571428</v>
+        <v>0</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>operating system</t>
+          <t>problem solve</t>
         </is>
       </c>
       <c r="B299" t="n">
@@ -5088,27 +5119,27 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>optimize</t>
+          <t>problem solving</t>
         </is>
       </c>
       <c r="B300" t="n">
-        <v>0</v>
+        <v>-0.0714285714285714</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>organizational</t>
+          <t>problem-solving</t>
         </is>
       </c>
       <c r="B301" t="n">
-        <v>0</v>
+        <v>0.2727272727272727</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>organizational skill</t>
+          <t>production systems</t>
         </is>
       </c>
       <c r="B302" t="n">
@@ -5118,27 +5149,27 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>ownership</t>
+          <t>programming</t>
         </is>
       </c>
       <c r="B303" t="n">
-        <v>0.6428571428571428</v>
+        <v>-0.0714285714285714</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>passionate</t>
+          <t>programming language</t>
         </is>
       </c>
       <c r="B304" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>penetration testing</t>
+          <t>programming languages</t>
         </is>
       </c>
       <c r="B305" t="n">
@@ -5148,67 +5179,67 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>performance optimization</t>
+          <t>project support</t>
         </is>
       </c>
       <c r="B306" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>php</t>
+          <t>prototype</t>
         </is>
       </c>
       <c r="B307" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>pipelines</t>
+          <t>python</t>
         </is>
       </c>
       <c r="B308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>postgres</t>
+          <t>pytorch</t>
         </is>
       </c>
       <c r="B309" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>postgresql</t>
+          <t>qa testing</t>
         </is>
       </c>
       <c r="B310" t="n">
-        <v>0.8275862068965517</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>postman</t>
+          <t>qa tools</t>
         </is>
       </c>
       <c r="B311" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>power bi</t>
+          <t>quality assurance</t>
         </is>
       </c>
       <c r="B312" t="n">
@@ -5218,67 +5249,67 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>preprocess</t>
+          <t>rabbitmq</t>
         </is>
       </c>
       <c r="B313" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>razor</t>
         </is>
       </c>
       <c r="B314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>problem solving</t>
+          <t>rdbms</t>
         </is>
       </c>
       <c r="B315" t="n">
-        <v>0.2727272727272727</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>problem-solving</t>
+          <t>redis</t>
         </is>
       </c>
       <c r="B316" t="n">
-        <v>0.2727272727272727</v>
+        <v>1</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>production systems</t>
+          <t>regression testing</t>
         </is>
       </c>
       <c r="B317" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>programming</t>
+          <t>relational database</t>
         </is>
       </c>
       <c r="B318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>programming language</t>
+          <t>reporting</t>
         </is>
       </c>
       <c r="B319" t="n">
@@ -5288,7 +5319,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>programming languages</t>
+          <t>research</t>
         </is>
       </c>
       <c r="B320" t="n">
@@ -5298,27 +5329,27 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>project support</t>
+          <t>responsibility</t>
         </is>
       </c>
       <c r="B321" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>python</t>
+          <t>responsible</t>
         </is>
       </c>
       <c r="B322" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>pytorch</t>
+          <t>rest</t>
         </is>
       </c>
       <c r="B323" t="n">
@@ -5328,7 +5359,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>qa testing</t>
+          <t>rest api</t>
         </is>
       </c>
       <c r="B324" t="n">
@@ -5338,7 +5369,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>qa tools</t>
+          <t>reusable code</t>
         </is>
       </c>
       <c r="B325" t="n">
@@ -5348,7 +5379,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>quality assurance</t>
+          <t>risk assessment</t>
         </is>
       </c>
       <c r="B326" t="n">
@@ -5358,7 +5389,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>rabbitmq</t>
+          <t>risk management</t>
         </is>
       </c>
       <c r="B327" t="n">
@@ -5368,7 +5399,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>razor</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="B328" t="n">
@@ -5378,27 +5409,27 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>rdbms</t>
+          <t>root cause analysis</t>
         </is>
       </c>
       <c r="B329" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>redis</t>
+          <t>scala</t>
         </is>
       </c>
       <c r="B330" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>regression testing</t>
+          <t>scalability</t>
         </is>
       </c>
       <c r="B331" t="n">
@@ -5408,7 +5439,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>relational database</t>
+          <t>scalable</t>
         </is>
       </c>
       <c r="B332" t="n">
@@ -5418,7 +5449,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>reporting</t>
+          <t>scalable code</t>
         </is>
       </c>
       <c r="B333" t="n">
@@ -5428,17 +5459,17 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>scale</t>
         </is>
       </c>
       <c r="B334" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>responsibility</t>
+          <t>scheduling skill</t>
         </is>
       </c>
       <c r="B335" t="n">
@@ -5448,7 +5479,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>responsible</t>
+          <t>scikit-learn</t>
         </is>
       </c>
       <c r="B336" t="n">
@@ -5458,57 +5489,57 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>rest</t>
+          <t>scripting</t>
         </is>
       </c>
       <c r="B337" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>rest api</t>
+          <t>scripts</t>
         </is>
       </c>
       <c r="B338" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>reusable code</t>
+          <t>scrum</t>
         </is>
       </c>
       <c r="B339" t="n">
-        <v>1</v>
+        <v>0.6428571428571428</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>risk assessment</t>
+          <t>secure</t>
         </is>
       </c>
       <c r="B340" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>risk management</t>
+          <t>secure applications</t>
         </is>
       </c>
       <c r="B341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>security</t>
         </is>
       </c>
       <c r="B342" t="n">
@@ -5518,7 +5549,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>root cause analysis</t>
+          <t>security best practices</t>
         </is>
       </c>
       <c r="B343" t="n">
@@ -5528,7 +5559,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>routine reports</t>
+          <t>security device</t>
         </is>
       </c>
       <c r="B344" t="n">
@@ -5538,27 +5569,27 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>scala</t>
+          <t>security monitoring</t>
         </is>
       </c>
       <c r="B345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>scala (production use)</t>
+          <t>selenium</t>
         </is>
       </c>
       <c r="B346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>scalability</t>
+          <t>self-motivated</t>
         </is>
       </c>
       <c r="B347" t="n">
@@ -5568,7 +5599,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>scalable</t>
+          <t>server</t>
         </is>
       </c>
       <c r="B348" t="n">
@@ -5578,7 +5609,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>scalable code</t>
+          <t>server operation system</t>
         </is>
       </c>
       <c r="B349" t="n">
@@ -5588,7 +5619,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>scalable systems</t>
+          <t>server side</t>
         </is>
       </c>
       <c r="B350" t="n">
@@ -5598,7 +5629,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>scheduling skill</t>
+          <t>server-side applications</t>
         </is>
       </c>
       <c r="B351" t="n">
@@ -5608,7 +5639,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>scikit-learn</t>
+          <t>soap</t>
         </is>
       </c>
       <c r="B352" t="n">
@@ -5618,17 +5649,17 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>scripting</t>
+          <t>social media</t>
         </is>
       </c>
       <c r="B353" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>scrum</t>
+          <t>social media crawler</t>
         </is>
       </c>
       <c r="B354" t="n">
@@ -5638,7 +5669,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>scrum methodology</t>
+          <t>software</t>
         </is>
       </c>
       <c r="B355" t="n">
@@ -5648,7 +5679,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>secure</t>
+          <t>software applications</t>
         </is>
       </c>
       <c r="B356" t="n">
@@ -5658,7 +5689,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>secure applications</t>
+          <t>software design</t>
         </is>
       </c>
       <c r="B357" t="n">
@@ -5668,7 +5699,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>security</t>
+          <t>software developers</t>
         </is>
       </c>
       <c r="B358" t="n">
@@ -5678,17 +5709,17 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>security best practices</t>
+          <t>software development</t>
         </is>
       </c>
       <c r="B359" t="n">
-        <v>0</v>
+        <v>0.3181818181818182</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>security monitoring</t>
+          <t>software engineering</t>
         </is>
       </c>
       <c r="B360" t="n">
@@ -5698,47 +5729,47 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>selenium</t>
+          <t>software engineering best practices</t>
         </is>
       </c>
       <c r="B361" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>self-motivated</t>
+          <t>software maintenance</t>
         </is>
       </c>
       <c r="B362" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>server</t>
+          <t>software programming</t>
         </is>
       </c>
       <c r="B363" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>server operation system</t>
+          <t>software security</t>
         </is>
       </c>
       <c r="B364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>server-side applications</t>
+          <t>software support</t>
         </is>
       </c>
       <c r="B365" t="n">
@@ -5748,17 +5779,17 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>soap</t>
+          <t>software testing</t>
         </is>
       </c>
       <c r="B366" t="n">
-        <v>0</v>
+        <v>0.6428571428571428</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>soap)</t>
+          <t>source control</t>
         </is>
       </c>
       <c r="B367" t="n">
@@ -5768,17 +5799,17 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>social media crawler</t>
+          <t>spark</t>
         </is>
       </c>
       <c r="B368" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>spring boot</t>
         </is>
       </c>
       <c r="B369" t="n">
@@ -5788,7 +5819,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>software analysis</t>
+          <t>spring boot framework</t>
         </is>
       </c>
       <c r="B370" t="n">
@@ -5798,37 +5829,37 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>software applications</t>
+          <t>sql</t>
         </is>
       </c>
       <c r="B371" t="n">
-        <v>0</v>
+        <v>0.7619047619047619</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>software developers</t>
+          <t>sql database</t>
         </is>
       </c>
       <c r="B372" t="n">
-        <v>0</v>
+        <v>0.6428571428571428</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>software development</t>
+          <t>sql server</t>
         </is>
       </c>
       <c r="B373" t="n">
-        <v>-0.1111111111111112</v>
+        <v>0.6428571428571428</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>software development cycle</t>
+          <t>statistics</t>
         </is>
       </c>
       <c r="B374" t="n">
@@ -5838,7 +5869,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>software engineer</t>
+          <t>strong troubleshooting</t>
         </is>
       </c>
       <c r="B375" t="n">
@@ -5848,7 +5879,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>software engineering</t>
+          <t>superset</t>
         </is>
       </c>
       <c r="B376" t="n">
@@ -5858,7 +5889,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>software engineering best practices</t>
+          <t>supervision</t>
         </is>
       </c>
       <c r="B377" t="n">
@@ -5868,7 +5899,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>software maintenance</t>
+          <t>support</t>
         </is>
       </c>
       <c r="B378" t="n">
@@ -5878,47 +5909,47 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>software programming</t>
+          <t>support business</t>
         </is>
       </c>
       <c r="B379" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>software security</t>
+          <t>switch</t>
         </is>
       </c>
       <c r="B380" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>software support</t>
+          <t>switches</t>
         </is>
       </c>
       <c r="B381" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>software testing</t>
+          <t>switching</t>
         </is>
       </c>
       <c r="B382" t="n">
-        <v>0.6428571428571428</v>
+        <v>1</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>source control</t>
+          <t>switching cisco</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -5928,27 +5959,27 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>spark</t>
+          <t>system architecture</t>
         </is>
       </c>
       <c r="B384" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>spring boot</t>
+          <t>system control</t>
         </is>
       </c>
       <c r="B385" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>spring boot framework</t>
+          <t>system fixes</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -5958,37 +5989,37 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>sql</t>
+          <t>system integration</t>
         </is>
       </c>
       <c r="B387" t="n">
-        <v>0.7619047619047619</v>
+        <v>0</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>sql database</t>
+          <t>system integration test</t>
         </is>
       </c>
       <c r="B388" t="n">
-        <v>0.6428571428571428</v>
+        <v>0</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>sql server</t>
+          <t>system monitor</t>
         </is>
       </c>
       <c r="B389" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>stakeholder communication</t>
+          <t>system software</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -5998,27 +6029,27 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>statistics</t>
+          <t>system testing</t>
         </is>
       </c>
       <c r="B391" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>strong troubleshooting</t>
+          <t>t-sql</t>
         </is>
       </c>
       <c r="B392" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>superset</t>
+          <t>tableau</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -6028,7 +6059,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>support</t>
+          <t>tableu</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -6038,7 +6069,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>switch</t>
+          <t>task prioritization</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -6048,7 +6079,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>switches</t>
+          <t>team leader</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -6058,7 +6089,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>switching</t>
+          <t>teamwork</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -6068,7 +6099,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>switching cisco</t>
+          <t>technical support</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -6078,37 +6109,37 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>system architecture</t>
+          <t>technical support engineer</t>
         </is>
       </c>
       <c r="B399" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>system control</t>
+          <t>technological developments</t>
         </is>
       </c>
       <c r="B400" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>system fixes</t>
+          <t>telerik</t>
         </is>
       </c>
       <c r="B401" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>system integration test</t>
+          <t>tensorflow</t>
         </is>
       </c>
       <c r="B402" t="n">
@@ -6118,27 +6149,27 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>system testing</t>
+          <t>test</t>
         </is>
       </c>
       <c r="B403" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>system vulnerabilities</t>
+          <t>test automation</t>
         </is>
       </c>
       <c r="B404" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>t-sql</t>
+          <t>test case</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -6148,7 +6179,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>tableau</t>
+          <t>test scenarios</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -6158,7 +6189,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>tableu</t>
+          <t>testable</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -6168,7 +6199,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>task prioritization</t>
+          <t>testable code</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -6178,7 +6209,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>team leader</t>
+          <t>testing</t>
         </is>
       </c>
       <c r="B409" t="n">
@@ -6188,27 +6219,27 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>teamwork</t>
+          <t>testing methodologies</t>
         </is>
       </c>
       <c r="B410" t="n">
-        <v>0.6428571428571428</v>
+        <v>0</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>technical support</t>
+          <t>time management</t>
         </is>
       </c>
       <c r="B411" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>technical support engineer</t>
+          <t>transform data</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -6218,47 +6249,47 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>technological developments</t>
+          <t>troubleshooting</t>
         </is>
       </c>
       <c r="B413" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>telerik</t>
+          <t>troubleshooting skill</t>
         </is>
       </c>
       <c r="B414" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>tensorflow</t>
+          <t>typography</t>
         </is>
       </c>
       <c r="B415" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>test automation</t>
+          <t>ui/ux</t>
         </is>
       </c>
       <c r="B416" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>test case</t>
+          <t>ui/ux design</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -6268,7 +6299,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>test case creation</t>
+          <t>unit testing</t>
         </is>
       </c>
       <c r="B418" t="n">
@@ -6278,7 +6309,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>test scenarios</t>
+          <t>unit tests</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -6288,7 +6319,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>test scripts</t>
+          <t>usability test</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -6298,27 +6329,27 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>testable code</t>
+          <t>usability testing</t>
         </is>
       </c>
       <c r="B421" t="n">
-        <v>0</v>
+        <v>0.6428571428571428</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>testing</t>
+          <t>user experience</t>
         </is>
       </c>
       <c r="B422" t="n">
-        <v>0</v>
+        <v>0.6428571428571428</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>testing methodologies</t>
+          <t>user feedback</t>
         </is>
       </c>
       <c r="B423" t="n">
@@ -6328,27 +6359,27 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>time management</t>
+          <t>user interface</t>
         </is>
       </c>
       <c r="B424" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>troubleshooting</t>
+          <t>user research</t>
         </is>
       </c>
       <c r="B425" t="n">
-        <v>-0.0869565217391306</v>
+        <v>1</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>troubleshooting skill</t>
+          <t>ux</t>
         </is>
       </c>
       <c r="B426" t="n">
@@ -6358,7 +6389,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>ui/ux</t>
+          <t>vba</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -6368,7 +6399,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>ui/ux design</t>
+          <t>version control</t>
         </is>
       </c>
       <c r="B428" t="n">
@@ -6378,7 +6409,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>unit testing</t>
+          <t>version control system</t>
         </is>
       </c>
       <c r="B429" t="n">
@@ -6388,17 +6419,17 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>unit tests</t>
+          <t>visual studio</t>
         </is>
       </c>
       <c r="B430" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>up to date</t>
+          <t>visualizations</t>
         </is>
       </c>
       <c r="B431" t="n">
@@ -6408,37 +6439,37 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>usability test</t>
+          <t>vm</t>
         </is>
       </c>
       <c r="B432" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>usability testing</t>
+          <t>vps</t>
         </is>
       </c>
       <c r="B433" t="n">
-        <v>0.6428571428571428</v>
+        <v>1</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>user experience</t>
+          <t>vsts</t>
         </is>
       </c>
       <c r="B434" t="n">
-        <v>0.6428571428571428</v>
+        <v>1</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>user feedback</t>
+          <t>vulnerabilities</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -6448,17 +6479,17 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>user interface</t>
+          <t>wcf</t>
         </is>
       </c>
       <c r="B436" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>user research</t>
+          <t>web api</t>
         </is>
       </c>
       <c r="B437" t="n">
@@ -6468,27 +6499,27 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>ux</t>
+          <t>web app</t>
         </is>
       </c>
       <c r="B438" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>vba</t>
+          <t>web application</t>
         </is>
       </c>
       <c r="B439" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>version control</t>
+          <t>web applications</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -6498,7 +6529,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>version control system</t>
+          <t>web backend services</t>
         </is>
       </c>
       <c r="B441" t="n">
@@ -6508,7 +6539,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>visual studio</t>
+          <t>web design</t>
         </is>
       </c>
       <c r="B442" t="n">
@@ -6518,7 +6549,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>visualizations</t>
+          <t>web development</t>
         </is>
       </c>
       <c r="B443" t="n">
@@ -6528,47 +6559,47 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>vm</t>
+          <t>web scraping</t>
         </is>
       </c>
       <c r="B444" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>vps</t>
+          <t>web service framework</t>
         </is>
       </c>
       <c r="B445" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>vsts</t>
+          <t>web service frameworks</t>
         </is>
       </c>
       <c r="B446" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>wcf</t>
+          <t>web services</t>
         </is>
       </c>
       <c r="B447" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>wcf (rest</t>
+          <t>web technologies</t>
         </is>
       </c>
       <c r="B448" t="n">
@@ -6578,17 +6609,17 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>web api</t>
+          <t>webscraping</t>
         </is>
       </c>
       <c r="B449" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>web app</t>
+          <t>wireframes</t>
         </is>
       </c>
       <c r="B450" t="n">
@@ -6598,27 +6629,27 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>web app development</t>
+          <t>wordpress</t>
         </is>
       </c>
       <c r="B451" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>web applications</t>
+          <t>work together</t>
         </is>
       </c>
       <c r="B452" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>web backend services</t>
+          <t>workflows</t>
         </is>
       </c>
       <c r="B453" t="n">
@@ -6628,17 +6659,17 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>web design</t>
+          <t>working experience</t>
         </is>
       </c>
       <c r="B454" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>web development</t>
+          <t>write</t>
         </is>
       </c>
       <c r="B455" t="n">
@@ -6648,110 +6679,10 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>web scraping</t>
+          <t>write english</t>
         </is>
       </c>
       <c r="B456" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="457">
-      <c r="A457" t="inlineStr">
-        <is>
-          <t>web service framework</t>
-        </is>
-      </c>
-      <c r="B457" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="458">
-      <c r="A458" t="inlineStr">
-        <is>
-          <t>web service frameworks</t>
-        </is>
-      </c>
-      <c r="B458" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="459">
-      <c r="A459" t="inlineStr">
-        <is>
-          <t>web services</t>
-        </is>
-      </c>
-      <c r="B459" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="460">
-      <c r="A460" t="inlineStr">
-        <is>
-          <t>web technologies</t>
-        </is>
-      </c>
-      <c r="B460" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="461">
-      <c r="A461" t="inlineStr">
-        <is>
-          <t>webscraping</t>
-        </is>
-      </c>
-      <c r="B461" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="462">
-      <c r="A462" t="inlineStr">
-        <is>
-          <t>wireframes</t>
-        </is>
-      </c>
-      <c r="B462" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="463">
-      <c r="A463" t="inlineStr">
-        <is>
-          <t>wordpress</t>
-        </is>
-      </c>
-      <c r="B463" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="464">
-      <c r="A464" t="inlineStr">
-        <is>
-          <t>work independently</t>
-        </is>
-      </c>
-      <c r="B464" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="465">
-      <c r="A465" t="inlineStr">
-        <is>
-          <t>work together</t>
-        </is>
-      </c>
-      <c r="B465" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="466">
-      <c r="A466" t="inlineStr">
-        <is>
-          <t>working experience</t>
-        </is>
-      </c>
-      <c r="B466" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6954,27 +6885,28 @@
           <t>machine learning
 monitoring
 deployment
+collaborates
 performance analysis
 algorithms</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G4" t="n">
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5">
@@ -7604,7 +7536,8 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>physical design</t>
+          <t>audit
+physical design</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -7614,16 +7547,16 @@
         <v>13</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
         <v>0.07140000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1333</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="17">
@@ -7709,26 +7642,27 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ethical reviews</t>
+          <t>audit
+ethical reviews</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>0.1667</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="19">
@@ -7765,26 +7699,28 @@
 supply chain
 management
 investigation
-integrate</t>
+collaborates
+integrate
+organisational policy</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="I19" t="n">
         <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6667</v>
+        <v>0.8235</v>
       </c>
     </row>
     <row r="20">
@@ -10163,22 +10099,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>120</v>
+        <v>167</v>
       </c>
       <c r="C2" t="n">
-        <v>299</v>
+        <v>252</v>
       </c>
       <c r="D2" t="n">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2779</v>
+        <v>0.4095</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6028</v>
+        <v>0.7493</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3744</v>
+        <v>0.5184</v>
       </c>
     </row>
     <row r="3">
@@ -10188,22 +10124,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C3" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>0.311</v>
+        <v>0.3344</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7883</v>
+        <v>0.7917</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4224</v>
+        <v>0.4473</v>
       </c>
     </row>
   </sheetData>
